--- a/data/trans_bre/IP42B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 32,15</t>
+          <t>-9,03; 33,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 37,32</t>
+          <t>-2,73; 38,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 13,7</t>
+          <t>-12,51; 14,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 340,99</t>
+          <t>-32,78; 450,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 228,9</t>
+          <t>-11,91; 236,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,89; 277,52</t>
+          <t>-72,39; 330,92</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 2,64</t>
+          <t>-5,9; 2,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 5,42</t>
+          <t>-8,5; 5,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 6,05</t>
+          <t>-3,37; 6,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 91,79</t>
+          <t>-79,1; 114,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 57,22</t>
+          <t>-51,41; 65,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 139,1</t>
+          <t>-40,31; 142,52</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 23,59</t>
+          <t>-5,18; 22,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 17,33</t>
+          <t>-7,06; 18,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 11,89</t>
+          <t>-10,15; 11,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-95,66; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 548,59</t>
+          <t>-83,41; 471,46</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,95</t>
+          <t>-3,06; 7,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 8,27</t>
+          <t>-4,45; 7,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,9</t>
+          <t>-3,02; 5,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 136,04</t>
+          <t>-33,99; 141,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 78,12</t>
+          <t>-26,24; 65,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 79,35</t>
+          <t>-34,51; 102,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 33,74</t>
+          <t>-12,7; 33,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 38,27</t>
+          <t>-3,03; 36,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 14,31</t>
+          <t>-12,83; 13,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 450,0</t>
+          <t>-47,66; 337,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 236,1</t>
+          <t>-11,99; 216,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 330,92</t>
+          <t>-76,59; 272,46</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 2,84</t>
+          <t>-6,06; 3,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 5,63</t>
+          <t>-8,02; 5,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 6,48</t>
+          <t>-3,2; 5,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-79,1; 114,65</t>
+          <t>-81,67; 122,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 65,5</t>
+          <t>-50,22; 59,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 142,52</t>
+          <t>-38,25; 134,92</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 22,67</t>
+          <t>-5,5; 22,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 18,45</t>
+          <t>-6,18; 18,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 11,15</t>
+          <t>-10,08; 10,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-95,66; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,41; 471,46</t>
+          <t>-84,4; 370,35</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,05</t>
+          <t>-3,26; 6,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 7,65</t>
+          <t>-4,14; 8,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,43</t>
+          <t>-2,95; 5,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 141,77</t>
+          <t>-35,8; 141,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 65,4</t>
+          <t>-24,52; 75,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 102,89</t>
+          <t>-32,07; 107,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 33,32</t>
+          <t>-11,65; 32,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 36,78</t>
+          <t>-3,29; 37,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 13,81</t>
+          <t>-12,46; 13,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 337,42</t>
+          <t>-38,38; 340,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 216,15</t>
+          <t>-10,58; 228,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,59; 272,46</t>
+          <t>-74,89; 277,52</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 3,22</t>
+          <t>-6,57; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 5,59</t>
+          <t>-8,4; 5,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,91</t>
+          <t>-3,59; 6,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-81,67; 122,55</t>
+          <t>-83,34; 91,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,22; 59,14</t>
+          <t>-49,44; 57,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 134,92</t>
+          <t>-43,79; 139,1</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 22,78</t>
+          <t>-5,33; 23,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 18,88</t>
+          <t>-7,29; 17,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 10,17</t>
+          <t>-9,29; 11,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,4; 370,35</t>
+          <t>-81,37; 548,59</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,83</t>
+          <t>-3,07; 6,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 8,18</t>
+          <t>-4,12; 8,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,68</t>
+          <t>-3,38; 4,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 141,98</t>
+          <t>-34,47; 136,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 75,67</t>
+          <t>-26,22; 78,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 107,39</t>
+          <t>-34,48; 79,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10,41</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16,54</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48,21%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>10.41150739757321</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>16.54331443664477</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.260319559233585</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.482136862328216</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.6473129101723235</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.02197732580830986</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-11,65; 32,15</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,29; 37,32</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-12,46; 13,7</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-38,38; 340,99</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-10,58; 228,9</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-74,89; 277,52</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-11.65428696232924</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.288080582484625</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-12.45605955602525</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.3837591067355768</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1058337090728303</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7488955068080814</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>32.14613323559243</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>37.31743987131443</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.70340228715292</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>3.409887662737908</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.289026299552546</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.775162945910323</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-33,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-11,23%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,57; 2,64</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-8,4; 5,42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,59; 6,05</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-83,34; 91,79</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-49,44; 57,22</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-43,79; 139,1</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.819790985522396</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.447420553906926</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.108443608857759</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.3357650406834366</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.112295178518933</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.165192558730608</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,32</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>125,02%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.565810893362708</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-8.395822987450039</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.586505022873512</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.8334060344008856</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4944004477038648</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4379181545442962</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,33; 23,59</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,29; 17,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,29; 11,89</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-81,37; 548,59</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.636294434318997</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.422536935078881</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.05262262492028</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.9179396075746193</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5721981004955189</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.390999863597638</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +767,153 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>6.316468728725681</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.969112586480914</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2043520091269901</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1.250189029047114</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.8694548434717525</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.02662091209883445</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,07; 6,95</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 8,27</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 4,9</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-34,47; 136,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-26,22; 78,12</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-34,48; 79,35</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.326339770170916</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.294803930162328</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-9.291898017738752</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.8136881915042581</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>23.58929319450062</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>17.33488382313871</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.88763988891035</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>5.485864403151371</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.869401378026056</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.756605808189621</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9371912646043784</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.2555066936809234</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1251437078747213</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1251257214923607</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.066655213804931</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.115552503575893</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.381218104972041</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.3447460209054771</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2622286282783215</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3447813496249396</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.949389186567315</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.269951233547307</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.899031766782712</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1.360435599647229</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7811743054328715</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7934584600859568</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +922,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
